--- a/reports/pdf_rolling5_20260923.xlsx
+++ b/reports/pdf_rolling5_20260923.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,836억   ·   현금 59억(1.2%)      오늘 2026-09-23  vs  5일전 2026-09-16      매수 15종목  /  매도 18종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,836억   ·   현금 40억(0.8%)      오늘 2026-09-23  vs  5일전 2026-09-16      매수 15종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -987,23 +987,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1133558834</v>
+        <v>-1766107877</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.77%→0.44%</t>
+          <t>0.59%→0.37%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>112→73</t>
+          <t>78→39</t>
         </is>
       </c>
     </row>
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1766107877</v>
+        <v>-1133558834</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.37%</t>
+          <t>0.77%→0.44%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>78→39</t>
+          <t>112→73</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-875142735</v>
+        <v>-2722545043</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.99%→0.68%</t>
+          <t>2.89%→1.95%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>52→41</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-2722545043</v>
+        <v>-875142735</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>2.89%→1.95%</t>
+          <t>0.99%→0.68%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>52→41</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,249억   ·   현금 178억(5.3%)      오늘 2026-09-23  vs  5일전 2026-09-16      매수 0종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,249억   ·   현금 119억(3.6%)      오늘 2026-09-23  vs  5일전 2026-09-16      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1519,7 +1519,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,638억   ·   현금 128억(4.7%)      오늘 2026-09-23  vs  5일전 2026-09-16      매수 1종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,638억   ·   현금 85억(3.2%)      오늘 2026-09-23  vs  5일전 2026-09-16      매수 1종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1708,7 +1708,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,983억   ·   현금 47억(2.3%)      오늘 2026-09-23  vs  5일전 2026-09-16      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,983억   ·   현금 31억(1.6%)      오늘 2026-09-23  vs  5일전 2026-09-16      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -2001,7 +2001,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 289억   ·   현금 3억(1.2%)      오늘 2026-09-23  vs  5일전 2026-09-16      매수 9종목  /  매도 12종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 289억   ·   현금 2억(0.8%)      오늘 2026-09-23  vs  5일전 2026-09-16      매수 9종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2287,23 +2287,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-32497519</v>
+        <v>-166110095</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2.71%→2.60%</t>
+          <t>3.42%→2.84%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>361→346</t>
+          <t>89→74</t>
         </is>
       </c>
     </row>
@@ -2331,23 +2331,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-166110095</v>
+        <v>-32497519</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>3.42%→2.84%</t>
+          <t>2.71%→2.60%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>89→74</t>
+          <t>361→346</t>
         </is>
       </c>
     </row>
@@ -2491,23 +2491,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-62202036</v>
+        <v>-54726031</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>2.91%→2.70%</t>
+          <t>2.47%→2.28%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
@@ -2519,23 +2519,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-54726031</v>
+        <v>-10668006</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2.47%→2.28%</t>
+          <t>0.14%→0.10%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>22→16</t>
         </is>
       </c>
     </row>
@@ -2547,23 +2547,23 @@
       <c r="E60" s="17" t="n"/>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-10668006</v>
+        <v>-62202036</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>0.14%→0.10%</t>
+          <t>2.91%→2.70%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>22→16</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260923.xlsx
+++ b/reports/pdf_rolling5_20260923.xlsx
@@ -855,23 +855,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-65</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-4836001852</v>
+        <v>-1850576709</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>1.78%→0.88%</t>
+          <t>0.54%→0.08%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>122→57</t>
+          <t>78→13</t>
         </is>
       </c>
     </row>
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-65</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1850576709</v>
+        <v>-4836001852</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.08%</t>
+          <t>1.78%→0.88%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>78→13</t>
+          <t>122→57</t>
         </is>
       </c>
     </row>
@@ -987,23 +987,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1766107877</v>
+        <v>-1133558834</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.37%</t>
+          <t>0.77%→0.44%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>78→39</t>
+          <t>112→73</t>
         </is>
       </c>
     </row>
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1133558834</v>
+        <v>-1766107877</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.77%→0.44%</t>
+          <t>0.59%→0.37%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>112→73</t>
+          <t>78→39</t>
         </is>
       </c>
     </row>
@@ -2287,23 +2287,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-166110095</v>
+        <v>-32497519</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>3.42%→2.84%</t>
+          <t>2.71%→2.60%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>89→74</t>
+          <t>361→346</t>
         </is>
       </c>
     </row>
@@ -2331,23 +2331,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-32497519</v>
+        <v>-166110095</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>2.71%→2.60%</t>
+          <t>3.42%→2.84%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>361→346</t>
+          <t>89→74</t>
         </is>
       </c>
     </row>
@@ -2491,23 +2491,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-54726031</v>
+        <v>-10668006</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>2.47%→2.28%</t>
+          <t>0.14%→0.10%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>22→16</t>
         </is>
       </c>
     </row>
@@ -2519,23 +2519,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-10668006</v>
+        <v>-54726031</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>0.14%→0.10%</t>
+          <t>2.47%→2.28%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>22→16</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260923.xlsx
+++ b/reports/pdf_rolling5_20260923.xlsx
@@ -2287,23 +2287,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-32497519</v>
+        <v>-166110095</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2.71%→2.60%</t>
+          <t>3.42%→2.84%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>361→346</t>
+          <t>89→74</t>
         </is>
       </c>
     </row>
@@ -2331,23 +2331,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-166110095</v>
+        <v>-32497519</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>3.42%→2.84%</t>
+          <t>2.71%→2.60%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>89→74</t>
+          <t>361→346</t>
         </is>
       </c>
     </row>
@@ -2491,23 +2491,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-10668006</v>
+        <v>-54726031</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>0.14%→0.10%</t>
+          <t>2.47%→2.28%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>22→16</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
@@ -2519,23 +2519,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-54726031</v>
+        <v>-62202036</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2.47%→2.28%</t>
+          <t>2.91%→2.70%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>
@@ -2547,23 +2547,23 @@
       <c r="E60" s="17" t="n"/>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-62202036</v>
+        <v>-10668006</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>2.91%→2.70%</t>
+          <t>0.14%→0.10%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>22→16</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260923.xlsx
+++ b/reports/pdf_rolling5_20260923.xlsx
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-2722545043</v>
+        <v>-875142735</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2.89%→1.95%</t>
+          <t>0.99%→0.68%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>52→41</t>
         </is>
       </c>
     </row>
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-875142735</v>
+        <v>-2722545043</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.99%→0.68%</t>
+          <t>2.89%→1.95%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>52→41</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
